--- a/Questions - Round 4.xlsx
+++ b/Questions - Round 4.xlsx
@@ -1,14 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_113672F89E3E5670C5D1BF3086324B62E5F5FC76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0025A087-EC66-4BD8-856C-7117340D56C0}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zander.fias\OneDrive - Innochem\OneDrive_1_25-9-2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B85ED7-83C8-4280-B37C-FCDAB1FAC7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
+    <sheet name="NL" sheetId="2" r:id="rId2"/>
+    <sheet name="FR" sheetId="3" r:id="rId3"/>
+    <sheet name="GE" sheetId="4" r:id="rId4"/>
+    <sheet name="SP" sheetId="5" r:id="rId5"/>
+    <sheet name="IT" sheetId="6" r:id="rId6"/>
+    <sheet name="PL" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="434">
   <si>
     <t>type</t>
   </si>
@@ -253,13 +264,1093 @@
   </si>
   <si>
     <t>Respectful behaviour supports dignity at work. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Wat is de kerngedachte achter SDG 8 – Waardig werk en economische groei?</t>
+  </si>
+  <si>
+    <t>Makkelijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Het is alleen een marketingslogan zonder praktische betekenis.</t>
+  </si>
+  <si>
+    <t>Het vraagt bedrijven om langetermijneffecten te negeren.</t>
+  </si>
+  <si>
+    <t>Het is alleen van toepassing op nationale overheden.</t>
+  </si>
+  <si>
+    <t>Het richt zich op waardig werk en duurzame groei.</t>
+  </si>
+  <si>
+    <t>SDG 8 gaat over waardig werk en duurzame groei en over het omzetten van dat doel in praktische actie. SDG 8 wordt nuttig wanneer mensen het brede doel vertalen naar praktische beslissingen.</t>
+  </si>
+  <si>
+    <t>Waarom is SDG 8 relevant voor een bedrijf dat chemicaliën distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Omdat eerlijke arbeidsvoorwaarden, veiligheid en bedrijfsveerkracht op lange termijn de duurzaamheidsprestaties kunnen beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG’s alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen thuishoort in jaarverslagen.</t>
+  </si>
+  <si>
+    <t>Omdat chemicaliën geen verband houden met duurzaamheid.</t>
+  </si>
+  <si>
+    <t>Eerlijke arbeidsvoorwaarden, veiligheid en bedrijfsveerkracht op lange termijn zijn praktische gebieden waarop een bedrijf het verschil kan maken. De SDG’s verbinden wereldwijde doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 8?</t>
+  </si>
+  <si>
+    <t>SDG 8 kan worden gekoppeld aan dagelijkse beslissingen.</t>
+  </si>
+  <si>
+    <t>Economische groei moet mensen en arbeidsomstandigheden negeren.</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen bijdragen via kleine gewoonten.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>Dit is het misverstand: het maakt de SDG te beperkt en verbergt praktische kansen. Een goede quizvraag stelt vaak een misvatting ter discussie, omdat dit de leerervaring beter doet beklijven.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 8 het best om van theorie naar actie?</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die uitvoeren.</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn rond duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Waarom is SDG 8 een nuttig leerthema voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het maakt deskundige kennis overbodig.</t>
+  </si>
+  <si>
+    <t>Het geeft één perfect antwoord voor elke situatie.</t>
+  </si>
+  <si>
+    <t>Het staat los van de bedrijfscultuur.</t>
+  </si>
+  <si>
+    <t>Het koppelt wereldwijde uitdagingen aan keuzes die mensen herkennen op het werk en thuis.</t>
+  </si>
+  <si>
+    <t>De krachtigste leerervaring ontstaat wanneer mensen het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG’s zijn het boeiendst wanneer ze relevant, concreet en verbonden met de rol van mensen aanvoelen.</t>
+  </si>
+  <si>
+    <t>Wat zegt het rapport over de naleving van het minimumloon?</t>
+  </si>
+  <si>
+    <t>Medewerkers ontvangen een loon dat gelijk is aan of hoger is dan het toepasselijke minimumloon.</t>
+  </si>
+  <si>
+    <t>Alleen tijdelijke medewerkers worden betaald.</t>
+  </si>
+  <si>
+    <t>Er wordt geen rekening gehouden met het minimumloon.</t>
+  </si>
+  <si>
+    <t>Het loon staat los van wettelijke vereisten.</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat medewerkers een beloning ontvangen die voldoet aan of hoger is dan de toepasselijke minimumloonvereisten. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welk percentage van de medewerkers valt onder collectieve arbeidsovereenkomsten?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>100% in elke divisie</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt een dekking door collectieve arbeidsovereenkomsten van 59% op Groepsniveau. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak over gezinsgerelateerd verlof wordt gerapporteerd?</t>
+  </si>
+  <si>
+    <t>Alleen het topmanagement kan verlof opnemen.</t>
+  </si>
+  <si>
+    <t>Gezinsverlof wordt niet bijgehouden.</t>
+  </si>
+  <si>
+    <t>100% van de medewerkers heeft recht op gezinsgerelateerd verlof.</t>
+  </si>
+  <si>
+    <t>Geen enkele medewerker kan gezinsverlof opnemen.</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat alle medewerkers recht hebben op gezinsgerelateerd verlof. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Wat ondersteunt in het privéleven indirect waardig werk?</t>
+  </si>
+  <si>
+    <t>Altijd de goedkoopste optie kiezen, ongeacht de omstandigheden.</t>
+  </si>
+  <si>
+    <t>Aannemen dat arbeidsrechten er niet toe doen.</t>
+  </si>
+  <si>
+    <t>Negeren hoe producten worden gemaakt.</t>
+  </si>
+  <si>
+    <t>Waar mogelijk producten en diensten kiezen van verantwoordelijke bedrijven.</t>
+  </si>
+  <si>
+    <t>Consumentenkeuzes kunnen meer verantwoorde bedrijfspraktijken ondersteunen. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Welk dagelijks gedrag weerspiegelt de waarden van waardig werk?</t>
+  </si>
+  <si>
+    <t>Mensen die diensten verlenen met respect behandelen.</t>
+  </si>
+  <si>
+    <t>Werknemers behandelen alsof ze onzichtbaar zijn.</t>
+  </si>
+  <si>
+    <t>Onveilige sluiproutes aanmoedigen.</t>
+  </si>
+  <si>
+    <t>Eerlijke behandeling negeren.</t>
+  </si>
+  <si>
+    <t>Respectvol gedrag ondersteunt waardigheid op het werk. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Quelle est l’idée principale de l’ODD 8 – Travail décent et croissance économique ?</t>
+  </si>
+  <si>
+    <t>Facile · Choix unique</t>
+  </si>
+  <si>
+    <t>Il s’agit uniquement d’un slogan marketing sans signification pratique.</t>
+  </si>
+  <si>
+    <t>Il demande aux entreprises d’ignorer les impacts à long terme.</t>
+  </si>
+  <si>
+    <t>Il s’applique uniquement aux gouvernements nationaux.</t>
+  </si>
+  <si>
+    <t>Il met l’accent sur le travail décent et la croissance durable.</t>
+  </si>
+  <si>
+    <t>L’ODD 8 porte sur le travail décent et la croissance durable, ainsi que sur la transformation de cet objectif en actions concrètes. L’ODD 8 devient utile lorsque les personnes traduisent cet objectif général en décisions pratiques.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’ODD 8 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que l’emploi équitable, la sécurité et la résilience à long terme de l’entreprise peuvent influencer ses performances en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité n’a sa place que dans les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n’ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>L’emploi équitable, la sécurité et la résilience à long terme de l’entreprise sont des domaines concrets dans lesquels une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante au sujet de l’ODD 8 ?</t>
+  </si>
+  <si>
+    <t>L’ODD 8 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>La croissance économique doit ignorer les personnes et les conditions de travail.</t>
+  </si>
+  <si>
+    <t>Les employés peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>C’est l’idée fausse : elle réduit excessivement la portée de l’ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée reçue, car cela rend l’apprentissage mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement permet le mieux de faire passer l’ODD 8 de la théorie à l’action ?</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu’un d’autre règle tous les problèmes.</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne vérifie.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mener à bien.</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Une action concrète favorise l’apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’ODD 8 est-il un thème d’apprentissage utile pour les employés ?</t>
+  </si>
+  <si>
+    <t>Il supprime le besoin de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>Il fournit une réponse parfaite à chaque situation.</t>
+  </si>
+  <si>
+    <t>Il n’a aucun rapport avec la culture d’entreprise.</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>L’apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et les choix qui leur sont familiers. Les ODD sont les plus engageants lorsqu’ils paraissent pertinents, concrets et liés au rôle de chacun.</t>
+  </si>
+  <si>
+    <t>Que dit le rapport au sujet du respect du salaire minimum ?</t>
+  </si>
+  <si>
+    <t>Les employés reçoivent un salaire égal ou supérieur au salaire minimum applicable.</t>
+  </si>
+  <si>
+    <t>Seuls les travailleurs temporaires sont rémunérés.</t>
+  </si>
+  <si>
+    <t>Le salaire minimum n’est pas pris en compte.</t>
+  </si>
+  <si>
+    <t>La rémunération n’a aucun rapport avec les exigences légales.</t>
+  </si>
+  <si>
+    <t>Le rapport indique que les employés reçoivent une rémunération qui atteint ou dépasse les exigences applicables en matière de salaire minimum. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe contribuent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quel pourcentage des employés est couvert par des conventions collectives ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>100% dans chaque division</t>
+  </si>
+  <si>
+    <t>Le rapport indique une couverture par des conventions collectives de 59% au niveau du Groupe. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe contribuent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quelle déclaration relative aux congés familiaux figure dans le rapport ?</t>
+  </si>
+  <si>
+    <t>Seuls les membres de la direction peuvent prendre un congé.</t>
+  </si>
+  <si>
+    <t>Les congés familiaux ne font pas l’objet d’un suivi.</t>
+  </si>
+  <si>
+    <t>100% des employés ont droit à un congé familial.</t>
+  </si>
+  <si>
+    <t>Aucun employé ne peut prendre de congé familial.</t>
+  </si>
+  <si>
+    <t>Le rapport indique que tous les employés ont droit à un congé familial. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe contribuent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Dans la vie privée, qu’est-ce qui soutient indirectement le travail décent ?</t>
+  </si>
+  <si>
+    <t>Toujours choisir l’option la moins chère, quelles que soient les conditions.</t>
+  </si>
+  <si>
+    <t>Supposer que les droits du travail n’ont pas d’importance.</t>
+  </si>
+  <si>
+    <t>Ignorer la manière dont les produits sont fabriqués.</t>
+  </si>
+  <si>
+    <t>Choisir, lorsque c’est possible, des produits et services provenant d’entreprises responsables.</t>
+  </si>
+  <si>
+    <t>Les choix des consommateurs peuvent soutenir des pratiques commerciales plus responsables. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu’ils sont répétés par un grand nombre de personnes.</t>
+  </si>
+  <si>
+    <t>Quel comportement quotidien reflète les valeurs du travail décent ?</t>
+  </si>
+  <si>
+    <t>Traiter avec respect les personnes qui fournissent des services.</t>
+  </si>
+  <si>
+    <t>Traiter les travailleurs comme s’ils étaient invisibles.</t>
+  </si>
+  <si>
+    <t>Encourager les raccourcis dangereux.</t>
+  </si>
+  <si>
+    <t>Ignorer le traitement équitable.</t>
+  </si>
+  <si>
+    <t>Un comportement respectueux favorise la dignité au travail. Les habitudes personnelles comptent, car de nombreux petits choix prennent tout leur sens lorsqu’ils sont répétés par un grand nombre de personnes.</t>
+  </si>
+  <si>
+    <t>Was ist der Kerngedanke von SDG 8 – Menschenwürdige Arbeit und Wirtschaftswachstum?</t>
+  </si>
+  <si>
+    <t>Leicht · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es ist lediglich ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf menschenwürdige Arbeit und nachhaltiges Wachstum.</t>
+  </si>
+  <si>
+    <t>Bei SDG 8 geht es um menschenwürdige Arbeit und nachhaltiges Wachstum sowie darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 8 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 8 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil faire Beschäftigung, Sicherheit und langfristige Widerstandsfähigkeit des Unternehmens die Nachhaltigkeitsleistung beeinflussen können.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Faire Beschäftigung, Sicherheit und langfristige Widerstandsfähigkeit des Unternehmens sind praktische Bereiche, in denen ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 8?</t>
+  </si>
+  <si>
+    <t>SDG 8 kann mit täglichen Entscheidungen verknüpft werden.</t>
+  </si>
+  <si>
+    <t>Wirtschaftswachstum muss Menschen und Arbeitsbedingungen außer Acht lassen.</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten einen Beitrag leisten.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>Das ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Möglichkeiten. Eine gute Quizfrage hinterfragt häufig ein Missverständnis, weil dies den Lernerfolg einprägsamer macht.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 8 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles löst.</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand hinsieht.</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln schafft Lernerfahrungen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu praktischen Verhaltensänderungen führen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 8 ein nützliches Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Es liefert für jede Situation die eine perfekte Antwort.</t>
+  </si>
+  <si>
+    <t>Es hat keinen Bezug zur Unternehmenskultur.</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen aus Beruf und Alltag kennen.</t>
+  </si>
+  <si>
+    <t>Am wirkungsvollsten ist Lernen, wenn Menschen die Verbindung zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind am ansprechendsten, wenn sie relevant und konkret wirken und mit den Aufgaben der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Was sagt der Bericht über die Einhaltung des Mindestlohns aus?</t>
+  </si>
+  <si>
+    <t>Die Mitarbeitenden erhalten eine Vergütung in Höhe des geltenden Mindestlohns oder darüber.</t>
+  </si>
+  <si>
+    <t>Nur Zeitarbeitskräfte werden bezahlt.</t>
+  </si>
+  <si>
+    <t>Der Mindestlohn wird nicht berücksichtigt.</t>
+  </si>
+  <si>
+    <t>Die Vergütung steht in keinem Zusammenhang mit gesetzlichen Anforderungen.</t>
+  </si>
+  <si>
+    <t>Im Bericht heißt es, dass die Mitarbeitenden eine Vergütung erhalten, die den geltenden Mindestlohnanforderungen entspricht oder darüber liegt. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent der Mitarbeitenden fallen unter Tarifverträge?</t>
+  </si>
+  <si>
+    <t>Schwer · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>100% in jeder Sparte</t>
+  </si>
+  <si>
+    <t>Der Bericht nennt auf Gruppenebene eine Tarifvertragsabdeckung von 59%. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Aussage zu familienbezogener Freistellung wird im Bericht genannt?</t>
+  </si>
+  <si>
+    <t>Nur die oberste Führungsebene kann Freistellung nehmen.</t>
+  </si>
+  <si>
+    <t>Familienbezogene Freistellung wird nicht erfasst.</t>
+  </si>
+  <si>
+    <t>100% der Mitarbeitenden haben Anspruch auf familienbezogene Freistellung.</t>
+  </si>
+  <si>
+    <t>Kein Mitarbeitender kann familienbezogene Freistellung nehmen.</t>
+  </si>
+  <si>
+    <t>Der Bericht besagt, dass alle Mitarbeitenden Anspruch auf familienbezogene Freistellung haben. Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Was unterstützt im Privatleben indirekt menschenwürdige Arbeit?</t>
+  </si>
+  <si>
+    <t>Unabhängig von den Bedingungen immer die billigste Option wählen.</t>
+  </si>
+  <si>
+    <t>Davon ausgehen, dass Arbeitnehmerrechte keine Rolle spielen.</t>
+  </si>
+  <si>
+    <t>Ignorieren, wie Produkte hergestellt werden.</t>
+  </si>
+  <si>
+    <t>Wenn möglich Produkte und Dienstleistungen verantwortungsbewusster Unternehmen wählen.</t>
+  </si>
+  <si>
+    <t>Konsumentscheidungen können verantwortungsvollere Geschäftspraktiken unterstützen. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Welches Alltagsverhalten spiegelt die Werte menschenwürdiger Arbeit wider?</t>
+  </si>
+  <si>
+    <t>Menschen, die Dienstleistungen erbringen, mit Respekt behandeln.</t>
+  </si>
+  <si>
+    <t>Beschäftigte so behandeln, als wären sie unsichtbar.</t>
+  </si>
+  <si>
+    <t>Unsichere Abkürzungen fördern.</t>
+  </si>
+  <si>
+    <t>Faire Behandlung ignorieren.</t>
+  </si>
+  <si>
+    <t>Respektvolles Verhalten unterstützt die Würde am Arbeitsplatz. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>¿Cuál es la idea principal del ODS 8 – Trabajo decente y crecimiento económico?</t>
+  </si>
+  <si>
+    <t>Fácil · Opción única</t>
+  </si>
+  <si>
+    <t>Es solo un eslogan de marketing sin significado práctico.</t>
+  </si>
+  <si>
+    <t>Pide a las empresas que ignoren los impactos a largo plazo.</t>
+  </si>
+  <si>
+    <t>Solo se aplica a los gobiernos nacionales.</t>
+  </si>
+  <si>
+    <t>Se centra en el trabajo decente y el crecimiento sostenible.</t>
+  </si>
+  <si>
+    <t>El ODS 8 trata sobre el trabajo decente y el crecimiento sostenible, y sobre convertir ese objetivo en acciones prácticas. El ODS 8 resulta útil cuando las personas traducen el objetivo general en decisiones concretas.</t>
+  </si>
+  <si>
+    <t>¿Por qué es relevante el ODS 8 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Medio · Opción única</t>
+  </si>
+  <si>
+    <t>Porque el empleo justo, la seguridad y la resiliencia empresarial a largo plazo pueden influir en el desempeño en materia de sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo tiene cabida en los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>El empleo justo, la seguridad y la resiliencia empresarial a largo plazo son áreas prácticas en las que una empresa puede marcar la diferencia. Los ODS conectan los objetivos globales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido común sobre el ODS 8?</t>
+  </si>
+  <si>
+    <t>El ODS 8 puede vincularse con las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>El crecimiento económico debe ignorar a las personas y las condiciones laborales.</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: hace que el ODS sea demasiado limitado y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar una idea errónea, porque así el aprendizaje resulta memorable.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 8 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Esperar a que otra persona lo arregle todo.</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está comprobando.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio práctico de comportamiento.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 8 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura empresarial.</t>
+  </si>
+  <si>
+    <t>Vincula los retos globales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>El aprendizaje más sólido se produce cuando las personas ven la conexión entre los objetivos globales y las decisiones que les resultan familiares. Los ODS son más atractivos cuando se perciben relevantes, concretos y vinculados a las funciones de las personas.</t>
+  </si>
+  <si>
+    <t>¿Qué dice el informe sobre el cumplimiento del salario mínimo?</t>
+  </si>
+  <si>
+    <t>Los empleados reciben una remuneración igual o superior al salario mínimo aplicable.</t>
+  </si>
+  <si>
+    <t>Solo se paga a los trabajadores temporales.</t>
+  </si>
+  <si>
+    <t>No se tiene en cuenta el salario mínimo.</t>
+  </si>
+  <si>
+    <t>La remuneración no guarda relación con los requisitos legales.</t>
+  </si>
+  <si>
+    <t>El informe indica que los empleados reciben una remuneración que cumple o supera los requisitos de salario mínimo aplicables. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué porcentaje de empleados está cubierto por convenios colectivos?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>100% en cada división</t>
+  </si>
+  <si>
+    <t>El informe indica una cobertura de convenios colectivos del 59% a nivel del Grupo. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación relacionada con el permiso familiar aparece en el informe?</t>
+  </si>
+  <si>
+    <t>Solo la alta dirección puede disfrutar de permisos.</t>
+  </si>
+  <si>
+    <t>No se realiza un seguimiento de los permisos familiares.</t>
+  </si>
+  <si>
+    <t>El 100% de los empleados tiene derecho a disfrutar de permisos familiares.</t>
+  </si>
+  <si>
+    <t>Ningún empleado puede disfrutar de permisos familiares.</t>
+  </si>
+  <si>
+    <t>El informe indica que todos los empleados tienen derecho a disfrutar de permisos familiares. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>En la vida privada, ¿qué apoya indirectamente el trabajo decente?</t>
+  </si>
+  <si>
+    <t>Elegir siempre la opción más barata, independientemente de las condiciones.</t>
+  </si>
+  <si>
+    <t>Suponer que los derechos laborales no importan.</t>
+  </si>
+  <si>
+    <t>Ignorar cómo se fabrican los productos.</t>
+  </si>
+  <si>
+    <t>Elegir productos y servicios de empresas responsables siempre que sea posible.</t>
+  </si>
+  <si>
+    <t>Las decisiones de consumo pueden apoyar prácticas empresariales más responsables. Los hábitos personales importan porque muchas pequeñas decisiones adquieren significado cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento cotidiano refleja los valores del trabajo decente?</t>
+  </si>
+  <si>
+    <t>Tratar con respeto a las personas que prestan servicios.</t>
+  </si>
+  <si>
+    <t>Tratar a los trabajadores como si fueran invisibles.</t>
+  </si>
+  <si>
+    <t>Fomentar atajos inseguros.</t>
+  </si>
+  <si>
+    <t>Ignorar el trato justo.</t>
+  </si>
+  <si>
+    <t>El comportamiento respetuoso favorece la dignidad en el trabajo. Los hábitos personales importan porque muchas pequeñas decisiones adquieren significado cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>Jaka jest główna idea Celu Zrównoważonego Rozwoju 8 – Wzrost gospodarczy i godna praca?</t>
+  </si>
+  <si>
+    <t>Łatwe · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>To tylko slogan marketingowy bez praktycznego znaczenia.</t>
+  </si>
+  <si>
+    <t>Wzywa firmy do ignorowania długoterminowych skutków.</t>
+  </si>
+  <si>
+    <t>Dotyczy wyłącznie rządów krajowych.</t>
+  </si>
+  <si>
+    <t>Koncentruje się na godnej pracy i zrównoważonym wzroście.</t>
+  </si>
+  <si>
+    <t>Cel 8 dotyczy godnej pracy i zrównoważonego wzrostu oraz przekładania tego celu na praktyczne działania. Cel 8 staje się użyteczny, gdy ludzie przekładają ogólny cel na konkretne decyzje.</t>
+  </si>
+  <si>
+    <t>Dlaczego Cel 8 jest istotny dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Średnie · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Ponieważ sprawiedliwe zatrudnienie, bezpieczeństwo i długoterminowa odporność firmy mogą wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Ponieważ Cele Zrównoważonego Rozwoju zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój powinien pojawiać się tylko w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Sprawiedliwe zatrudnienie, bezpieczeństwo i długoterminowa odporność firmy to praktyczne obszary, w których przedsiębiorstwo może coś zmienić. Cele Zrównoważonego Rozwoju łączą globalne cele z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie jest częstym nieporozumieniem dotyczącym Celu 8?</t>
+  </si>
+  <si>
+    <t>Cel 8 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>Wzrost gospodarczy musi ignorować ludzi i warunki pracy.</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne nawyki.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i poprawiać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>To jest właśnie nieporozumienie: zawęża ono znaczenie Celu i ukrywa praktyczne możliwości. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu nauka lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada Cel 8 z teorii na działanie?</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Robienie czegoś przeciwnego, gdy nikt nie sprawdza.</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne jego wdrożenie.</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie umożliwia uczenie się i wymierną poprawę. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowania.</t>
+  </si>
+  <si>
+    <t>Dlaczego Cel 8 jest przydatnym tematem edukacyjnym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę posiadania wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź w każdej sytuacji.</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą firmy.</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami, które ludzie rozpoznają w pracy i w domu.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsza nauka ma miejsce wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi im wyborami. Cele Zrównoważonego Rozwoju najbardziej angażują, gdy są postrzegane jako istotne, konkretne i związane z rolami ludzi.</t>
+  </si>
+  <si>
+    <t>Co raport mówi o przestrzeganiu płacy minimalnej?</t>
+  </si>
+  <si>
+    <t>Pracownicy otrzymują wynagrodzenie równe obowiązującej płacy minimalnej lub wyższe.</t>
+  </si>
+  <si>
+    <t>Wynagrodzenie otrzymują tylko pracownicy tymczasowi.</t>
+  </si>
+  <si>
+    <t>Płaca minimalna nie jest brana pod uwagę.</t>
+  </si>
+  <si>
+    <t>Wynagrodzenie nie ma związku z wymogami prawnymi.</t>
+  </si>
+  <si>
+    <t>Raport stwierdza, że pracownicy otrzymują wynagrodzenie spełniające lub przekraczające obowiązujące wymogi dotyczące płacy minimalnej. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Jaki procent pracowników jest objęty układami zbiorowymi pracy?</t>
+  </si>
+  <si>
+    <t>Trudne · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>100% w każdym dziale</t>
+  </si>
+  <si>
+    <t>Raport podaje, że na poziomie Grupy układami zbiorowymi pracy objętych jest 59% pracowników. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie dotyczące urlopu rodzinnego znajduje się w raporcie?</t>
+  </si>
+  <si>
+    <t>Tylko najwyższa kadra kierownicza może skorzystać z urlopu.</t>
+  </si>
+  <si>
+    <t>Urlopy rodzinne nie są monitorowane.</t>
+  </si>
+  <si>
+    <t>100% pracowników ma prawo do urlopu związanego z obowiązkami rodzinnymi.</t>
+  </si>
+  <si>
+    <t>Żaden pracownik nie może skorzystać z urlopu rodzinnego.</t>
+  </si>
+  <si>
+    <t>Raport stwierdza, że wszyscy pracownicy mają prawo do urlopu związanego z obowiązkami rodzinnymi. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Co w życiu prywatnym pośrednio wspiera godną pracę?</t>
+  </si>
+  <si>
+    <t>Zawsze wybierać najtańszą opcję bez względu na warunki.</t>
+  </si>
+  <si>
+    <t>Zakładać, że prawa pracownicze nie mają znaczenia.</t>
+  </si>
+  <si>
+    <t>Ignorować sposób wytwarzania produktów.</t>
+  </si>
+  <si>
+    <t>W miarę możliwości wybierać produkty i usługi odpowiedzialnych firm.</t>
+  </si>
+  <si>
+    <t>Wybory konsumenckie mogą wspierać bardziej odpowiedzialne praktyki biznesowe. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Które codzienne zachowanie odzwierciedla wartości godnej pracy?</t>
+  </si>
+  <si>
+    <t>Traktowanie z szacunkiem osób świadczących usługi.</t>
+  </si>
+  <si>
+    <t>Traktowanie pracowników tak, jakby byli niewidoczni.</t>
+  </si>
+  <si>
+    <t>Zachęcanie do niebezpiecznych skrótów.</t>
+  </si>
+  <si>
+    <t>Ignorowanie sprawiedliwego traktowania.</t>
+  </si>
+  <si>
+    <t>Pełne szacunku zachowanie wspiera godność w pracy. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Qual è l’idea principale alla base dell’OSS 8 – Lavoro dignitoso e crescita economica?</t>
+  </si>
+  <si>
+    <t>Facile · Scelta singola</t>
+  </si>
+  <si>
+    <t>È solo uno slogan di marketing privo di significato pratico.</t>
+  </si>
+  <si>
+    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
+  </si>
+  <si>
+    <t>Si applica solo ai governi nazionali.</t>
+  </si>
+  <si>
+    <t>Si concentra sul lavoro dignitoso e sulla crescita sostenibile.</t>
+  </si>
+  <si>
+    <t>L’OSS 8 riguarda il lavoro dignitoso e la crescita sostenibile e la trasformazione di questo obiettivo in azioni concrete. L’OSS 8 diventa utile quando le persone traducono l’obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Perché l’OSS 8 è rilevante per un’azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Scelta singola</t>
+  </si>
+  <si>
+    <t>Perché un’occupazione equa, la sicurezza e la resilienza aziendale a lungo termine possono influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità appartiene solo alle relazioni annuali.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>Un’occupazione equa, la sicurezza e la resilienza aziendale a lungo termine sono ambiti concreti in cui un’azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull’OSS 8?</t>
+  </si>
+  <si>
+    <t>L’OSS 8 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>La crescita economica deve ignorare le persone e le condizioni di lavoro.</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: rende l’OSS troppo ristretto e nasconde opportunità pratiche. Una buona domanda di un quiz spesso mette in discussione un’idea errata, perché ciò rende l’apprendimento memorabile.</t>
+  </si>
+  <si>
+    <t>Quale comportamento trasforma meglio l’OSS 8 dalla teoria all’azione?</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Un’azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico dei comportamenti.</t>
+  </si>
+  <si>
+    <t>Cosa rende l’OSS 8 un tema di apprendimento utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>Fornisce un’unica risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Non è collegato alla cultura aziendale.</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali alle scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>L’apprendimento più efficace avviene quando le persone vedono il legame tra gli obiettivi globali e le scelte che conoscono. Gli OSS sono più coinvolgenti quando appaiono rilevanti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Cosa dice il rapporto sul rispetto del salario minimo?</t>
+  </si>
+  <si>
+    <t>I dipendenti ricevono una retribuzione pari o superiore al salario minimo applicabile.</t>
+  </si>
+  <si>
+    <t>Vengono retribuiti solo i lavoratori temporanei.</t>
+  </si>
+  <si>
+    <t>Il salario minimo non viene preso in considerazione.</t>
+  </si>
+  <si>
+    <t>La retribuzione non è collegata ai requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che i dipendenti ricevono una retribuzione pari o superiore ai requisiti applicabili in materia di salario minimo. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale percentuale di dipendenti è coperta da accordi di contrattazione collettiva?</t>
+  </si>
+  <si>
+    <t>Difficile · Scelta singola</t>
+  </si>
+  <si>
+    <t>100% in ogni divisione</t>
+  </si>
+  <si>
+    <t>Il rapporto indica una copertura della contrattazione collettiva del 59% a livello di Gruppo. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale affermazione relativa al congedo familiare è riportata?</t>
+  </si>
+  <si>
+    <t>Solo l’alta dirigenza può usufruire del congedo.</t>
+  </si>
+  <si>
+    <t>Il congedo familiare non viene monitorato.</t>
+  </si>
+  <si>
+    <t>Il 100% dei dipendenti ha diritto a usufruire del congedo familiare.</t>
+  </si>
+  <si>
+    <t>Nessun dipendente può usufruire del congedo familiare.</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che tutti i dipendenti hanno diritto a usufruire del congedo familiare. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Nella vita privata, cosa sostiene indirettamente il lavoro dignitoso?</t>
+  </si>
+  <si>
+    <t>Scegliere sempre l’opzione più economica, indipendentemente dalle condizioni.</t>
+  </si>
+  <si>
+    <t>Supporre che i diritti dei lavoratori non siano importanti.</t>
+  </si>
+  <si>
+    <t>Ignorare come vengono realizzati i prodotti.</t>
+  </si>
+  <si>
+    <t>Quando possibile, scegliere prodotti e servizi di aziende responsabili.</t>
+  </si>
+  <si>
+    <t>Le scelte dei consumatori possono sostenere pratiche aziendali più responsabili. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale comportamento quotidiano riflette i valori del lavoro dignitoso?</t>
+  </si>
+  <si>
+    <t>Trattare con rispetto le persone che forniscono servizi.</t>
+  </si>
+  <si>
+    <t>Trattare i lavoratori come se fossero invisibili.</t>
+  </si>
+  <si>
+    <t>Incoraggiare scorciatoie non sicure.</t>
+  </si>
+  <si>
+    <t>Ignorare un trattamento equo.</t>
+  </si>
+  <si>
+    <t>Un comportamento rispettoso sostiene la dignità sul lavoro. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,7 +1405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,9 +1419,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -343,6 +1440,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,6 +1460,120 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0791A980-7E55-44B2-B90C-1D9B2AA91FBA}" name="Questions3" displayName="Questions3" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{0791A980-7E55-44B2-B90C-1D9B2AA91FBA}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{27099E91-3F48-4B30-A4E5-E6134E873388}" name="type"/>
+    <tableColumn id="2" xr3:uid="{7102D1A2-6101-4884-8728-389D49C42B35}" name="question"/>
+    <tableColumn id="3" xr3:uid="{C5822EC7-402B-46BB-9217-D004E34D0ADC}" name="note"/>
+    <tableColumn id="4" xr3:uid="{67C118E7-B622-4845-B7C8-701511BBC1C8}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{D1383081-C65C-4F1F-BB2A-56D70D782162}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{1F8CCE95-B3AF-4BAB-9899-53000116FDA3}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{A235455B-0097-4D04-BEEB-C1C4A23E44DA}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{B53E3438-913B-4E98-95DD-3ADA818605FB}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{53839724-6212-429A-9346-2C663CFBB897}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{4D1DA152-21F4-4FB7-BAB6-837216B55485}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DB4E02F-A99F-44DC-A452-4B44CE524DEA}" name="Questions4" displayName="Questions4" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{6DB4E02F-A99F-44DC-A452-4B44CE524DEA}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{B2BBDE6A-8219-46C0-9007-49ABB6E96520}" name="type"/>
+    <tableColumn id="2" xr3:uid="{36FB428D-2469-4D66-9395-91F3C3E5F11E}" name="question"/>
+    <tableColumn id="3" xr3:uid="{5A131B69-6D06-478B-9F73-38F23C922B1B}" name="note"/>
+    <tableColumn id="4" xr3:uid="{DF63D01C-78BF-4FBC-8885-809A5A9B31CA}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{8491C931-D107-4F56-9B7B-A4BF409169E8}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{5E9ADC1A-498E-47D5-B062-29580C66EE8A}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{4AC1D83C-A31F-49A5-AC13-8FA9EC5D26CE}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{AF9B4B33-05D9-4F0A-BA91-106D894D5094}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{2FBC7806-72A5-468B-8BAF-AF849D1872D1}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{74C3A6F1-BF6A-4CDC-A340-B0D4BAD6FBC1}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D980A940-4FFC-4926-8B41-0732F8AB906A}" name="Questions5" displayName="Questions5" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{D980A940-4FFC-4926-8B41-0732F8AB906A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{7BD6A31A-F3C2-4D45-8C8F-42DCFB550E24}" name="type"/>
+    <tableColumn id="2" xr3:uid="{8B93E884-6F59-4F49-9220-77D1FEC20960}" name="question"/>
+    <tableColumn id="3" xr3:uid="{57104BB9-2F48-484A-A247-2FD79CBFDE84}" name="note"/>
+    <tableColumn id="4" xr3:uid="{1EB6A4BB-F4D7-4ED7-BA14-528159097A59}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{DF499C3B-6ABC-4D04-AA13-D97540939B82}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{2F23FCB4-D69E-4954-8571-74FC14895E85}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{EE508DC6-F5E1-4BDD-933D-5BBB2C9E42E9}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{EAD947F7-7B64-42E1-9608-E6D075B7AFD5}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{47AE47C3-F92E-41A5-B7A9-9600A94CE03B}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{B1AABB2E-6326-4FC9-BFF4-FFFD6B2006C8}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B019A78B-9F77-426E-B4C6-AEC2AADF87D1}" name="Questions6" displayName="Questions6" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{B019A78B-9F77-426E-B4C6-AEC2AADF87D1}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{0A7821EC-52E7-4672-AAD8-B3978F60DE59}" name="type"/>
+    <tableColumn id="2" xr3:uid="{29864877-3D21-4EE4-9958-EE22B404309C}" name="question"/>
+    <tableColumn id="3" xr3:uid="{3B29241C-89A5-4394-9831-55CAA393568C}" name="note"/>
+    <tableColumn id="4" xr3:uid="{3CF49025-7AB2-4609-AA81-EA9031B1205C}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{AF508536-5841-4108-AB54-8905A5A01D7D}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{16101579-72FA-45BB-A0F2-05633F74C43C}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{E7C6AFFB-7CB0-4BE9-A7F5-2E25E14DFFBC}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{1C936BB0-2740-4D51-914E-4CF55F8E3238}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{9FB592A7-B68C-4F97-ADC7-3ED65450D89D}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{2E2EB2E1-9D1A-4D16-A048-F4D0143A3D66}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{053DC767-333A-4653-A90A-C06DDFC51D03}" name="Questions8" displayName="Questions8" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{053DC767-333A-4653-A90A-C06DDFC51D03}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{554B4338-2A2C-4D75-8973-B8928338680E}" name="type"/>
+    <tableColumn id="2" xr3:uid="{919EEB60-CF29-4B36-95F0-F3E8DDB90B93}" name="question"/>
+    <tableColumn id="3" xr3:uid="{2205B4D1-49AF-4E40-80E4-D7AA7577A08A}" name="note"/>
+    <tableColumn id="4" xr3:uid="{7D61D265-AD9F-4DFB-9FEC-8A2F2D1077D7}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{FA33D682-5F98-49AB-A633-29238AD6AADF}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{459C0FF0-1E45-40B7-8F6C-0C79425B8A68}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{0F7A73E1-F71F-44D8-BB7C-2E68C5D85549}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{275AA7AE-0435-44E0-9864-C9194FCDF8D1}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{A0BE08B4-11D0-4A98-84EF-68DB565240C5}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{296C9152-8250-49F2-B729-7FCE7310437A}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{87E5FA2A-A39F-48EE-AE40-9E1759187383}" name="Questions7" displayName="Questions7" ref="A1:J11">
+  <autoFilter ref="A1:J11" xr:uid="{87E5FA2A-A39F-48EE-AE40-9E1759187383}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{CFEEA56B-B83E-4CA2-9386-FA0738F6C1A8}" name="type"/>
+    <tableColumn id="2" xr3:uid="{0F7B1C1F-8631-47C1-A0A9-0138C50A9E1A}" name="question"/>
+    <tableColumn id="3" xr3:uid="{2ECFF9E1-ED2D-43EC-8EEA-DE4CA1BA1C41}" name="note"/>
+    <tableColumn id="4" xr3:uid="{02EC5F02-7769-4E26-87AA-92315F9D098F}" name="option1"/>
+    <tableColumn id="5" xr3:uid="{E839A633-42D2-41FC-8ABB-E7A7A74E2755}" name="option2"/>
+    <tableColumn id="6" xr3:uid="{7D50B7A5-CBCE-46BC-B1B2-EED84F1685EA}" name="option3"/>
+    <tableColumn id="7" xr3:uid="{20B29F18-F4DF-4C15-909D-14C8627AEDA1}" name="option4"/>
+    <tableColumn id="8" xr3:uid="{07198CDE-2B84-4542-8318-955F8E6FC239}" name="correct"/>
+    <tableColumn id="9" xr3:uid="{321A6EEB-658E-4E3F-955F-3E2495455AFB}" name="explanation"/>
+    <tableColumn id="10" xr3:uid="{7AED3FDD-3DAC-4FC2-B7AB-E91108DC16FF}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -650,7 +1865,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -661,7 +1876,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +1908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -723,7 +1938,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -753,7 +1968,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -783,7 +1998,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -813,7 +2028,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -843,7 +2058,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -873,7 +2088,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -903,7 +2118,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -933,7 +2148,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -963,7 +2178,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1001,13 +2216,2138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A356C3A-2679-47DA-AE1E-6AE53709BC77}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC853D71-3770-49F4-98F2-43EB891B25C2}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="319" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6BB802-43D2-48C9-B122-F4EE8F9901C5}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44EB7E3-A0C2-4F94-8709-2B2478F28770}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D081102-AB6A-494B-BF7E-1FCF32902BDD}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AFBE40-83DC-45BA-AACF-7BAC88E831D9}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1175,23 +4515,46 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C4053A-B08E-40F8-8CC7-9931962AD930}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF63BDE6-B30F-4987-BA00-E8E977CCD7AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA5A654-5563-4BB8-8462-5A8368C016F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA5A654-5563-4BB8-8462-5A8368C016F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF63BDE6-B30F-4987-BA00-E8E977CCD7AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C4053A-B08E-40F8-8CC7-9931962AD930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Questions - Round 4.xlsx
+++ b/Questions - Round 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zander.fias\OneDrive - Innochem\OneDrive_1_25-9-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stockmeier.sharepoint.com/sites/YoungProfessionalsSTOCKMEIER-YPIII-SustainabilityAwarenessSessions/Freigegebene Dokumente/02. Content/Questions in template/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B85ED7-83C8-4280-B37C-FCDAB1FAC7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2148" yWindow="720" windowWidth="12732" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -1440,10 +1440,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1865,7 +1861,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -1876,7 +1872,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1908,7 +1904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1938,7 +1934,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1968,7 +1964,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1998,7 +1994,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2028,7 +2024,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2058,7 +2054,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2088,7 +2084,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2118,7 +2114,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2148,7 +2144,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2178,7 +2174,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2219,18 +2215,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A356C3A-2679-47DA-AE1E-6AE53709BC77}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2262,7 +2258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2322,7 +2318,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2352,7 +2348,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2382,7 +2378,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2412,7 +2408,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="315" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2442,7 +2438,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2502,7 +2498,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2532,7 +2528,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2573,18 +2569,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC853D71-3770-49F4-98F2-43EB891B25C2}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2616,7 +2612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2646,7 +2642,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2676,7 +2672,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2706,7 +2702,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="210" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2736,7 +2732,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2766,7 +2762,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="319" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="345" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2796,7 +2792,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2826,7 +2822,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2856,7 +2852,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2886,7 +2882,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2927,18 +2923,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6BB802-43D2-48C9-B122-F4EE8F9901C5}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2970,7 +2966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3000,7 +2996,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3030,7 +3026,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3060,7 +3056,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3090,7 +3086,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3120,7 +3116,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3150,7 +3146,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3180,7 +3176,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3210,7 +3206,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3240,7 +3236,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3281,18 +3277,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44EB7E3-A0C2-4F94-8709-2B2478F28770}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3324,7 +3320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3354,7 +3350,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3384,7 +3380,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3414,7 +3410,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="195" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3444,7 +3440,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3474,7 +3470,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="315" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3504,7 +3500,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3534,7 +3530,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3564,7 +3560,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3594,7 +3590,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3635,18 +3631,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D081102-AB6A-494B-BF7E-1FCF32902BDD}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3678,7 +3674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3708,7 +3704,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3738,7 +3734,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3768,7 +3764,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="195" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3798,7 +3794,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3828,7 +3824,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3858,7 +3854,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3888,7 +3884,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3918,7 +3914,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3948,7 +3944,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3989,18 +3985,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AFBE40-83DC-45BA-AACF-7BAC88E831D9}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4032,7 +4028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -4062,7 +4058,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="300" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -4092,7 +4088,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4122,7 +4118,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="210" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4152,7 +4148,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4182,7 +4178,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="261" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="285" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4212,7 +4208,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4242,7 +4238,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4272,7 +4268,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -4302,7 +4298,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4351,8 +4347,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff0b0af6195b7500cf034195288be193">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c14c416c1ab46b49649d30a0f512b68e" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -4397,7 +4402,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4424,8 +4429,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4514,27 +4519,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF63BDE6-B30F-4987-BA00-E8E977CCD7AF}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA5A654-5563-4BB8-8462-5A8368C016F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C4053A-B08E-40F8-8CC7-9931962AD930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBDCE50-D6A6-4393-A75A-F04D96387D07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -4549,12 +4559,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C4053A-B08E-40F8-8CC7-9931962AD930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>